--- a/output/pdf_financials_xlsx/VXL.xlsx
+++ b/output/pdf_financials_xlsx/VXL.xlsx
@@ -5747,16 +5747,16 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>-0.061</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0</v>
+        <v>-0.028</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>-0.026</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0</v>
+        <v>-0.032</v>
       </c>
       <c r="M91" s="3" t="n">
         <v>-0.073</v>
@@ -5789,37 +5789,37 @@
         <v>0.057986</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.113915</v>
+        <v>0.110617</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.112823</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.081855</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.113057</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.147551</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>1.761</v>
+        <v>3.308</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>2.224</v>
+        <v>3.6</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>2.425</v>
+        <v>4.335</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>3.62</v>
+        <v>4.436</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.358</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.324</v>
       </c>
       <c r="O92" s="3" t="n">
         <v>0</v>
@@ -5828,7 +5828,7 @@
         <v>0</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>0.07199999999999999</v>
       </c>
     </row>
     <row r="93">
@@ -9680,7 +9680,11 @@
           <t>Warrant reserve 9</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -11164,7 +11168,11 @@
           <t>Warrant reserve 7</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -11826,7 +11834,11 @@
           <t>Warrant reserve 10</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -12880,7 +12892,11 @@
           <t>Warrant reserve 11</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -13072,7 +13088,11 @@
           <t>Foreign currency transaction reserve</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -14908,7 +14928,11 @@
           <t>Warrant reserve (Note 11)</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -16768,7 +16792,11 @@
           <t>Warrant reserve (Note 12) 1,547</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -16964,7 +16992,11 @@
           <t>Foreign currency transaction reserve (61)</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -18600,7 +18632,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/VXL.xlsx
+++ b/output/pdf_financials_xlsx/VXL.xlsx
@@ -921,34 +921,34 @@
         <v>0.075546</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.410844</v>
+        <v>1.07</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>4.549</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>1.803</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>1.041</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0</v>
+        <v>1.143</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0</v>
+        <v>0.986</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.343</v>
+        <v>0.584</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.114</v>
+        <v>0.254</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.012</v>
+        <v>0.148</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0</v>
+        <v>0.179</v>
       </c>
     </row>
     <row r="11">
@@ -1005,7 +1005,7 @@
         <v>-0.196</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>0</v>
+        <v>-0.179</v>
       </c>
     </row>
     <row r="12">
@@ -1023,13 +1023,13 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.001506</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000566</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>4e-06</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1059,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>0</v>
@@ -1948,13 +1948,13 @@
         <v>-0.160927</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.446241</v>
+        <v>-0.447747</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.519446</v>
+        <v>-0.520012</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.433284</v>
+        <v>-0.433288</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.30271</v>
@@ -1984,7 +1984,7 @@
         <v>-0.254</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.178</v>
+        <v>-0.196</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>0.522</v>
@@ -2062,13 +2062,13 @@
         <v>-0.160927</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.446241</v>
+        <v>-0.447747</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.519446</v>
+        <v>-0.520012</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.433284</v>
+        <v>-0.433288</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.30271</v>
@@ -2098,7 +2098,7 @@
         <v>-0.254</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.178</v>
+        <v>-0.196</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>0.522</v>
@@ -2360,16 +2360,16 @@
         <v>0.416153</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.009738</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.000396</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.03546</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.111972</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>1.023</v>
@@ -2381,13 +2381,13 @@
         <v>0.753</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>2.241</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>0.9379999999999999</v>
@@ -2474,16 +2474,16 @@
         <v>0.416153</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.009738</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.000396</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.03546</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.111972</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>1.023</v>
@@ -2495,13 +2495,13 @@
         <v>0.753</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>2.241</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>0.9379999999999999</v>
@@ -3158,16 +3158,16 @@
         <v>0.023189</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.029749</v>
+        <v>0.020011</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.000396</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.249802</v>
+        <v>0.214342</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.11472</v>
+        <v>0.002748</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0.029</v>
@@ -3179,13 +3179,13 @@
         <v>0.075</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.11</v>
+        <v>0.027</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.283</v>
+        <v>0.042</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.541</v>
+        <v>0.031</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>0</v>
@@ -10980,7 +10980,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -15508,7 +15508,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -17774,7 +17774,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -44160,7 +44160,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -46164,7 +46164,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -46332,7 +46332,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -52816,7 +52816,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
@@ -55004,7 +55004,7 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">

--- a/output/pdf_financials_xlsx/VXL.xlsx
+++ b/output/pdf_financials_xlsx/VXL.xlsx
@@ -1308,7 +1308,7 @@
         <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.08064</v>
+        <v>-0.062988</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -2206,7 +2206,7 @@
         <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-18.07095269148285</v>
+        <v>-14.11524266035618</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -4293,19 +4293,19 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.0113</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.0135</v>
       </c>
       <c r="H67" s="3" t="n">
         <v>0</v>
@@ -6265,7 +6265,7 @@
         </is>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002239</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>-0.011558</v>
@@ -39106,7 +39106,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E322" t="inlineStr">
         <is>
           <t>-</t>
@@ -40946,7 +40950,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
           <t>-</t>
@@ -41140,7 +41148,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
           <t>-</t>
@@ -41428,7 +41440,11 @@
           <t>HST/GST recoverable</t>
         </is>
       </c>
-      <c r="D346" t="inlineStr"/>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E346" t="inlineStr">
         <is>
           <t>-</t>
@@ -43182,7 +43198,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D364" t="inlineStr"/>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E364" t="inlineStr">
         <is>
           <t>-</t>
@@ -55200,7 +55220,11 @@
           <t>Future income tax recovery (Note 11)</t>
         </is>
       </c>
-      <c r="D491" t="inlineStr"/>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E491" t="inlineStr">
         <is>
           <t>-</t>
